--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96273031</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713906.0805388401</v>
+        <v>713906</v>
       </c>
       <c r="R2" t="n">
-        <v>6652371.451219309</v>
+        <v>6652371</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +754,9 @@
           <t>2021-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,55 +782,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Törnquist, Kjell Håkan  Andersson </t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96273016</v>
+        <v>96273069</v>
       </c>
       <c r="B3" t="n">
-        <v>4964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101608</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713906.0805388401</v>
+        <v>713874</v>
       </c>
       <c r="R3" t="n">
-        <v>6652371.451219309</v>
+        <v>6652363</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,24 +860,9 @@
           <t>2021-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska gnagspår i barken på gammal asp. Även noterad fullt utvecklad asppraktbagge på aspen den 17/7-2021.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,63 +883,55 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Törnquist, Kjell Håkan  Andersson </t>
+          <t>Bo Törnquist, Kjell Håkan  Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96273069</v>
+        <v>105375192</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>219792</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Sund, S om, N om Mörtsjön, Upl</t>
+          <t>Kista havet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713874.3800746002</v>
+        <v>713983</v>
       </c>
       <c r="R4" t="n">
-        <v>6652363.087268597</v>
+        <v>6652443</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,34 +969,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Karolin Ring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Törnquist, Kjell Håkan  Andersson </t>
+          <t>Karolin Ring</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105374878</v>
+        <v>75724023</v>
       </c>
       <c r="B5" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,17 +1018,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gåsvik, Upl</t>
+          <t>Västerängen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713859.9814950825</v>
+        <v>713777</v>
       </c>
       <c r="R5" t="n">
-        <v>6652411.95506022</v>
+        <v>6652393</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,27 +1072,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karolin Ring</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karolin Ring</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105375186</v>
+        <v>105374839</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,34 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gåsvik, Upl</t>
+          <t>Kista havet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713911.0371052767</v>
+        <v>713987</v>
       </c>
       <c r="R6" t="n">
-        <v>6652468.130079161</v>
+        <v>6652466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,19 +1152,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105375184</v>
+        <v>105374842</v>
       </c>
       <c r="B7" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,14 +1212,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gåsvik, Upl</t>
+          <t>Kista havet, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713895.3521143865</v>
+        <v>713789</v>
       </c>
       <c r="R7" t="n">
-        <v>6652374.343688681</v>
+        <v>6652354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,19 +1249,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,15 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105375179</v>
+        <v>105374873</v>
       </c>
       <c r="B8" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,14 +1309,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gåsvik, Upl</t>
+          <t>Kista havet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713867.9760518809</v>
+        <v>713972</v>
       </c>
       <c r="R8" t="n">
-        <v>6652386.814268329</v>
+        <v>6652412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,22 +1343,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,15 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105375177</v>
+        <v>105374878</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,21 +1386,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1535,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713850.6118646931</v>
+        <v>713860</v>
       </c>
       <c r="R9" t="n">
-        <v>6652417.436546029</v>
+        <v>6652412</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,22 +1440,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,15 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105375188</v>
+        <v>105375166</v>
       </c>
       <c r="B10" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,10 +1507,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713940.1693631441</v>
+        <v>713800</v>
       </c>
       <c r="R10" t="n">
-        <v>6652442.709030351</v>
+        <v>6652327</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,19 +1540,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,6 +1566,871 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105375179</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>713868</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6652387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105375184</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>713895</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6652374</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105375188</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>713940</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6652443</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105375174</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>713773</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6652373</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105375175</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>713790</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6652353</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105375177</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>713851</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6652418</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>105375186</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>713911</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6652468</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>105375176</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gåsvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>713792</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6652353</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>105375189</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kista havet, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>713969</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6652410</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96273031</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96273069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375192</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75724023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374839</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374842</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374873</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374878</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1566,6 +1611,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375166</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375179</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375184</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375188</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1954,6 +2019,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375174</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375175</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375177</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,6 +2325,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375186</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375176</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2431,8 +2521,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105375189</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,6 +2524,113 @@
       <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105375189</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135948595</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104808</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västerängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>713911</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6652360</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emma Gatu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135948595</t>
         </is>
       </c>
     </row>
@@ -2547,6 +2654,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104808</v>
+        <v>104828</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104828</v>
+        <v>104830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104830</v>
+        <v>104831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104831</v>
+        <v>104832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104832</v>
+        <v>104838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104838</v>
+        <v>104839</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104839</v>
+        <v>104850</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104850</v>
+        <v>104863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104863</v>
+        <v>104864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104864</v>
+        <v>104877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21922-2023 artfynd.xlsx
+++ b/artfynd/A 21922-2023 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>135948595</v>
       </c>
       <c r="B20" t="n">
-        <v>104877</v>
+        <v>104878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
